--- a/计分.xlsx
+++ b/计分.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\life\board_game\project_six_dynasty\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B771923D-0E4A-42A4-AAD3-30B736AA9A25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{906F756D-4909-4430-AFFC-AC91559021BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{8AF991C0-2FFC-4B9D-8DFA-610AA56EBD09}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="31">
   <si>
     <t>计分</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -146,6 +146,22 @@
   </si>
   <si>
     <t>紫色/王导</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v0.2_0521</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蓝色/桓温</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>绿色/chijian</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>紫色/祖逖</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -530,7 +546,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42E67ED8-6937-492E-8350-3FCD992CF871}">
-  <dimension ref="A1:P13"/>
+  <dimension ref="A1:P20"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.3">
@@ -837,16 +853,12 @@
       <c r="M11">
         <v>4</v>
       </c>
-      <c r="N11">
-        <f>CEILING(L$10/10,1)*M11</f>
-        <v>32</v>
-      </c>
       <c r="O11">
         <v>16</v>
       </c>
       <c r="P11">
         <f t="shared" si="2"/>
-        <v>127</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.3">
@@ -927,6 +939,164 @@
       <c r="P13">
         <f t="shared" si="2"/>
         <v>154</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>1</v>
+      </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
+      <c r="E16">
+        <v>12</v>
+      </c>
+      <c r="H16">
+        <v>5</v>
+      </c>
+      <c r="I16">
+        <v>6</v>
+      </c>
+      <c r="K16">
+        <v>110</v>
+      </c>
+      <c r="P16">
+        <f t="shared" ref="P16:P20" si="4">SUM(B16:O16)</f>
+        <v>134</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H17">
+        <v>12</v>
+      </c>
+      <c r="I17">
+        <v>14</v>
+      </c>
+      <c r="K17">
+        <v>72</v>
+      </c>
+      <c r="L17">
+        <f>SUM(H17:K17)</f>
+        <v>98</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>28</v>
+      </c>
+      <c r="H18">
+        <v>8</v>
+      </c>
+      <c r="I18">
+        <v>16</v>
+      </c>
+      <c r="J18">
+        <v>19</v>
+      </c>
+      <c r="K18">
+        <v>70</v>
+      </c>
+      <c r="M18">
+        <v>4</v>
+      </c>
+      <c r="N18">
+        <f>CEILING(L$17/10,1)*M11</f>
+        <v>40</v>
+      </c>
+      <c r="O18">
+        <v>30</v>
+      </c>
+      <c r="P18">
+        <f t="shared" si="4"/>
+        <v>187</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>29</v>
+      </c>
+      <c r="D19">
+        <v>4</v>
+      </c>
+      <c r="F19">
+        <v>12</v>
+      </c>
+      <c r="H19">
+        <v>5</v>
+      </c>
+      <c r="I19">
+        <v>10</v>
+      </c>
+      <c r="J19">
+        <v>19</v>
+      </c>
+      <c r="K19">
+        <v>59</v>
+      </c>
+      <c r="M19">
+        <v>4</v>
+      </c>
+      <c r="N19">
+        <f>CEILING(L$17/10,1)*M12</f>
+        <v>40</v>
+      </c>
+      <c r="O19">
+        <v>14</v>
+      </c>
+      <c r="P19">
+        <f t="shared" si="4"/>
+        <v>167</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>30</v>
+      </c>
+      <c r="B20">
+        <v>5</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20">
+        <v>18</v>
+      </c>
+      <c r="G20">
+        <v>9</v>
+      </c>
+      <c r="H20">
+        <v>7</v>
+      </c>
+      <c r="I20">
+        <v>10</v>
+      </c>
+      <c r="J20">
+        <v>20</v>
+      </c>
+      <c r="K20">
+        <v>55</v>
+      </c>
+      <c r="M20">
+        <v>4</v>
+      </c>
+      <c r="N20">
+        <f>CEILING(L$17/10,1)*M13</f>
+        <v>40</v>
+      </c>
+      <c r="O20">
+        <v>18</v>
+      </c>
+      <c r="P20">
+        <f t="shared" si="4"/>
+        <v>187</v>
       </c>
     </row>
   </sheetData>

--- a/计分.xlsx
+++ b/计分.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\life\board_game\project_six_dynasty\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{906F756D-4909-4430-AFFC-AC91559021BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{551EF9F1-C7DA-4D0B-9239-829D544BDF61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{8AF991C0-2FFC-4B9D-8DFA-610AA56EBD09}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="35">
   <si>
     <t>计分</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -162,6 +162,22 @@
   </si>
   <si>
     <t>紫色/祖逖</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v0.3_0530</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蓝色/祖逖</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>绿色/张轨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>紫色/桓温</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -546,7 +562,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42E67ED8-6937-492E-8350-3FCD992CF871}">
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:P27"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.3">
@@ -1015,7 +1031,7 @@
         <v>30</v>
       </c>
       <c r="P18">
-        <f t="shared" si="4"/>
+        <f>SUM(B18:O18)</f>
         <v>187</v>
       </c>
     </row>
@@ -1097,6 +1113,197 @@
       <c r="P20">
         <f t="shared" si="4"/>
         <v>187</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23">
+        <v>0</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>8</v>
+      </c>
+      <c r="I23">
+        <v>28</v>
+      </c>
+      <c r="J23">
+        <v>28</v>
+      </c>
+      <c r="K23">
+        <v>174</v>
+      </c>
+      <c r="P23">
+        <f t="shared" ref="P23" si="5">SUM(B23:O23)</f>
+        <v>238</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>2</v>
+      </c>
+      <c r="H24">
+        <v>12</v>
+      </c>
+      <c r="I24">
+        <v>24</v>
+      </c>
+      <c r="K24">
+        <v>127</v>
+      </c>
+      <c r="L24">
+        <f>SUM(H24:K24)</f>
+        <v>163</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25">
+        <v>1</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <v>2</v>
+      </c>
+      <c r="H25">
+        <v>2</v>
+      </c>
+      <c r="I25">
+        <v>2</v>
+      </c>
+      <c r="J25">
+        <v>15</v>
+      </c>
+      <c r="K25">
+        <v>94</v>
+      </c>
+      <c r="M25">
+        <v>4</v>
+      </c>
+      <c r="N25">
+        <f>CEILING(L24/10,1)*M25</f>
+        <v>68</v>
+      </c>
+      <c r="O25">
+        <v>32</v>
+      </c>
+      <c r="P25">
+        <f>SUM(B25:O25)</f>
+        <v>220</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26">
+        <v>3</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="D26">
+        <v>8</v>
+      </c>
+      <c r="E26">
+        <v>4</v>
+      </c>
+      <c r="G26">
+        <v>29</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>2</v>
+      </c>
+      <c r="J26">
+        <v>11</v>
+      </c>
+      <c r="K26">
+        <v>75</v>
+      </c>
+      <c r="M26">
+        <v>3</v>
+      </c>
+      <c r="N26">
+        <f>CEILING(L24/10,1)*M26</f>
+        <v>51</v>
+      </c>
+      <c r="O26">
+        <v>0</v>
+      </c>
+      <c r="P26">
+        <f t="shared" ref="P26:P27" si="6">SUM(B26:O26)</f>
+        <v>186</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27">
+        <v>4</v>
+      </c>
+      <c r="C27">
+        <v>2</v>
+      </c>
+      <c r="D27">
+        <v>2</v>
+      </c>
+      <c r="E27">
+        <v>7</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>22</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>4</v>
+      </c>
+      <c r="J27">
+        <v>25</v>
+      </c>
+      <c r="K27">
+        <v>91</v>
+      </c>
+      <c r="M27">
+        <v>4</v>
+      </c>
+      <c r="N27">
+        <f>CEILING(L24/10,1)*M27</f>
+        <v>68</v>
+      </c>
+      <c r="O27">
+        <v>6</v>
+      </c>
+      <c r="P27">
+        <f t="shared" si="6"/>
+        <v>235</v>
       </c>
     </row>
   </sheetData>

--- a/计分.xlsx
+++ b/计分.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\life\board_game\project_six_dynasty\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{551EF9F1-C7DA-4D0B-9239-829D544BDF61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1277F284-95E3-4D3D-9D77-886829F7D517}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{8AF991C0-2FFC-4B9D-8DFA-610AA56EBD09}"/>
   </bookViews>
@@ -16,6 +16,7 @@
     <sheet name="0516_game" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="47">
   <si>
     <t>计分</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -178,6 +179,54 @@
   </si>
   <si>
     <t>紫色/桓温</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v0.4_0604</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蓝色/谢安</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>绿色/桓温</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>紫色/张轨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>t9结束</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>t8结束</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v0.6_0613</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>t10结束</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黑色放完所有token</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黑色/拓拔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>绿色/王导</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>紫色/刘裕</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -562,7 +611,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42E67ED8-6937-492E-8350-3FCD992CF871}">
-  <dimension ref="A1:P27"/>
+  <dimension ref="A1:P41"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.3">
@@ -638,8 +687,8 @@
         <v>121</v>
       </c>
       <c r="P2">
-        <f>SUM(B2:O2)</f>
-        <v>158</v>
+        <f>SUM(E2:O2)</f>
+        <v>156</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
@@ -699,8 +748,8 @@
         <v>7</v>
       </c>
       <c r="P4">
-        <f t="shared" ref="P4:P6" si="0">SUM(B4:O4)</f>
-        <v>179</v>
+        <f>SUM(E4:O4)</f>
+        <v>177</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.3">
@@ -741,15 +790,15 @@
         <v>5</v>
       </c>
       <c r="N5">
-        <f t="shared" ref="N5:N6" si="1">CEILING(L$3/10,1)*M5</f>
+        <f>CEILING(L$3/10,1)*M5</f>
         <v>75</v>
       </c>
       <c r="O5">
         <v>12</v>
       </c>
       <c r="P5">
-        <f t="shared" si="0"/>
-        <v>204</v>
+        <f>SUM(E5:O5)</f>
+        <v>201</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.3">
@@ -778,15 +827,15 @@
         <v>5</v>
       </c>
       <c r="N6">
-        <f t="shared" si="1"/>
+        <f>CEILING(L$3/10,1)*M6</f>
         <v>75</v>
       </c>
       <c r="O6">
         <v>15</v>
       </c>
       <c r="P6">
-        <f t="shared" si="0"/>
-        <v>184</v>
+        <f>SUM(E6:O6)</f>
+        <v>181</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.3">
@@ -822,8 +871,8 @@
         <v>105</v>
       </c>
       <c r="P9">
-        <f t="shared" ref="P9:P13" si="2">SUM(B9:O9)</f>
-        <v>143</v>
+        <f>SUM(E9:O9)</f>
+        <v>142</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.3">
@@ -873,8 +922,8 @@
         <v>16</v>
       </c>
       <c r="P11">
-        <f t="shared" si="2"/>
-        <v>95</v>
+        <f>SUM(E11:O11)</f>
+        <v>94</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.3">
@@ -909,15 +958,15 @@
         <v>4</v>
       </c>
       <c r="N12">
-        <f t="shared" ref="N12:N13" si="3">CEILING(L$10/10,1)*M12</f>
+        <f>CEILING(L$10/10,1)*M12</f>
         <v>32</v>
       </c>
       <c r="O12">
         <v>22</v>
       </c>
       <c r="P12">
-        <f t="shared" si="2"/>
-        <v>151</v>
+        <f>SUM(E12:O12)</f>
+        <v>149</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.3">
@@ -946,15 +995,15 @@
         <v>4</v>
       </c>
       <c r="N13">
-        <f t="shared" si="3"/>
+        <f>CEILING(L$10/10,1)*M13</f>
         <v>32</v>
       </c>
       <c r="O13">
         <v>25</v>
       </c>
       <c r="P13">
-        <f t="shared" si="2"/>
-        <v>154</v>
+        <f>SUM(E13:O13)</f>
+        <v>153</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.3">
@@ -982,8 +1031,8 @@
         <v>110</v>
       </c>
       <c r="P16">
-        <f t="shared" ref="P16:P20" si="4">SUM(B16:O16)</f>
-        <v>134</v>
+        <f>SUM(E16:O16)</f>
+        <v>133</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.3">
@@ -1031,7 +1080,7 @@
         <v>30</v>
       </c>
       <c r="P18">
-        <f>SUM(B18:O18)</f>
+        <f>SUM(E18:O18)</f>
         <v>187</v>
       </c>
     </row>
@@ -1068,8 +1117,8 @@
         <v>14</v>
       </c>
       <c r="P19">
-        <f t="shared" si="4"/>
-        <v>167</v>
+        <f>SUM(E19:O19)</f>
+        <v>163</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.3">
@@ -1111,14 +1160,17 @@
         <v>18</v>
       </c>
       <c r="P20">
-        <f t="shared" si="4"/>
-        <v>187</v>
+        <f>SUM(E20:O20)</f>
+        <v>181</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>31</v>
       </c>
+      <c r="B22" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
@@ -1146,7 +1198,7 @@
         <v>174</v>
       </c>
       <c r="P23">
-        <f t="shared" ref="P23" si="5">SUM(B23:O23)</f>
+        <f>SUM(E23:O23)</f>
         <v>238</v>
       </c>
     </row>
@@ -1207,8 +1259,8 @@
         <v>32</v>
       </c>
       <c r="P25">
-        <f>SUM(B25:O25)</f>
-        <v>220</v>
+        <f>SUM(E25:O25)</f>
+        <v>219</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.3">
@@ -1253,8 +1305,8 @@
         <v>0</v>
       </c>
       <c r="P26">
-        <f t="shared" ref="P26:P27" si="6">SUM(B26:O26)</f>
-        <v>186</v>
+        <f>SUM(E26:O26)</f>
+        <v>175</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.3">
@@ -1302,8 +1354,363 @@
         <v>6</v>
       </c>
       <c r="P27">
-        <f t="shared" si="6"/>
-        <v>235</v>
+        <f>SUM(E27:O27)</f>
+        <v>227</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>35</v>
+      </c>
+      <c r="B29" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>1</v>
+      </c>
+      <c r="C30">
+        <v>2</v>
+      </c>
+      <c r="F30">
+        <v>7</v>
+      </c>
+      <c r="H30">
+        <v>4</v>
+      </c>
+      <c r="I30">
+        <v>12</v>
+      </c>
+      <c r="J30">
+        <v>10</v>
+      </c>
+      <c r="K30">
+        <v>163</v>
+      </c>
+      <c r="P30">
+        <f>SUM(E30:O30)</f>
+        <v>196</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>2</v>
+      </c>
+      <c r="H31">
+        <v>13</v>
+      </c>
+      <c r="I31">
+        <v>22</v>
+      </c>
+      <c r="K31">
+        <v>90</v>
+      </c>
+      <c r="L31">
+        <f>SUM(H31:K31)</f>
+        <v>125</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>36</v>
+      </c>
+      <c r="B32">
+        <v>4</v>
+      </c>
+      <c r="D32">
+        <v>1</v>
+      </c>
+      <c r="E32">
+        <v>4</v>
+      </c>
+      <c r="G32">
+        <v>7</v>
+      </c>
+      <c r="H32">
+        <v>1</v>
+      </c>
+      <c r="I32">
+        <v>4</v>
+      </c>
+      <c r="J32">
+        <v>31</v>
+      </c>
+      <c r="K32">
+        <v>65</v>
+      </c>
+      <c r="M32">
+        <v>4</v>
+      </c>
+      <c r="N32">
+        <f>CEILING(L31/10,1)*M32</f>
+        <v>52</v>
+      </c>
+      <c r="O32">
+        <v>30</v>
+      </c>
+      <c r="P32">
+        <f>SUM(E32:O32)</f>
+        <v>198</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>37</v>
+      </c>
+      <c r="B33">
+        <v>2</v>
+      </c>
+      <c r="D33">
+        <v>5</v>
+      </c>
+      <c r="E33">
+        <v>2</v>
+      </c>
+      <c r="G33">
+        <v>16</v>
+      </c>
+      <c r="H33">
+        <v>1</v>
+      </c>
+      <c r="I33">
+        <v>6</v>
+      </c>
+      <c r="J33">
+        <v>28</v>
+      </c>
+      <c r="K33">
+        <v>122</v>
+      </c>
+      <c r="M33">
+        <v>3</v>
+      </c>
+      <c r="N33">
+        <f>CEILING(L31/10,1)*M33</f>
+        <v>39</v>
+      </c>
+      <c r="O33">
+        <v>26</v>
+      </c>
+      <c r="P33">
+        <f>SUM(E33:O33)</f>
+        <v>243</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>38</v>
+      </c>
+      <c r="C34">
+        <v>1</v>
+      </c>
+      <c r="D34">
+        <v>2</v>
+      </c>
+      <c r="F34">
+        <v>4</v>
+      </c>
+      <c r="G34">
+        <v>11</v>
+      </c>
+      <c r="H34">
+        <v>7</v>
+      </c>
+      <c r="I34">
+        <v>14</v>
+      </c>
+      <c r="J34">
+        <v>29</v>
+      </c>
+      <c r="K34">
+        <v>91</v>
+      </c>
+      <c r="M34">
+        <v>4</v>
+      </c>
+      <c r="N34">
+        <f>CEILING(L31/10,1)*M34</f>
+        <v>52</v>
+      </c>
+      <c r="O34">
+        <v>34</v>
+      </c>
+      <c r="P34">
+        <f>SUM(E34:O34)</f>
+        <v>246</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>41</v>
+      </c>
+      <c r="B36" t="s">
+        <v>42</v>
+      </c>
+      <c r="C36" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>44</v>
+      </c>
+      <c r="H37">
+        <v>20</v>
+      </c>
+      <c r="I37">
+        <v>46</v>
+      </c>
+      <c r="J37">
+        <v>33</v>
+      </c>
+      <c r="K37">
+        <v>149</v>
+      </c>
+      <c r="P37">
+        <f>SUM(E37:O37)</f>
+        <v>248</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>2</v>
+      </c>
+      <c r="H38">
+        <v>10</v>
+      </c>
+      <c r="I38">
+        <v>16</v>
+      </c>
+      <c r="K38">
+        <v>104</v>
+      </c>
+      <c r="L38">
+        <f>SUM(H38:K38)</f>
+        <v>130</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>28</v>
+      </c>
+      <c r="B39">
+        <v>2</v>
+      </c>
+      <c r="D39">
+        <v>1</v>
+      </c>
+      <c r="E39">
+        <v>11</v>
+      </c>
+      <c r="G39">
+        <v>4</v>
+      </c>
+      <c r="I39">
+        <v>6</v>
+      </c>
+      <c r="J39">
+        <v>27</v>
+      </c>
+      <c r="K39">
+        <v>72</v>
+      </c>
+      <c r="M39">
+        <v>4</v>
+      </c>
+      <c r="N39">
+        <f>CEILING(L38/10,1)*M39</f>
+        <v>52</v>
+      </c>
+      <c r="O39">
+        <v>10</v>
+      </c>
+      <c r="P39">
+        <f>SUM(E39:O39)</f>
+        <v>186</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>45</v>
+      </c>
+      <c r="B40">
+        <v>1</v>
+      </c>
+      <c r="C40">
+        <v>2</v>
+      </c>
+      <c r="D40">
+        <v>2</v>
+      </c>
+      <c r="E40">
+        <v>7</v>
+      </c>
+      <c r="F40">
+        <v>22</v>
+      </c>
+      <c r="G40">
+        <v>7</v>
+      </c>
+      <c r="I40">
+        <v>4</v>
+      </c>
+      <c r="J40">
+        <v>29</v>
+      </c>
+      <c r="K40">
+        <v>95</v>
+      </c>
+      <c r="M40">
+        <v>1</v>
+      </c>
+      <c r="N40">
+        <f>CEILING(L38/10,1)*M40</f>
+        <v>13</v>
+      </c>
+      <c r="O40">
+        <v>8</v>
+      </c>
+      <c r="P40">
+        <f>SUM(E40:O40)</f>
+        <v>186</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>46</v>
+      </c>
+      <c r="C41">
+        <v>7</v>
+      </c>
+      <c r="F41">
+        <v>29</v>
+      </c>
+      <c r="H41">
+        <v>2</v>
+      </c>
+      <c r="I41">
+        <v>6</v>
+      </c>
+      <c r="J41">
+        <v>28</v>
+      </c>
+      <c r="K41">
+        <v>90</v>
+      </c>
+      <c r="M41">
+        <v>7</v>
+      </c>
+      <c r="N41">
+        <f>CEILING(L38/10,1)*M41</f>
+        <v>91</v>
+      </c>
+      <c r="O41">
+        <v>16</v>
+      </c>
+      <c r="P41">
+        <f>SUM(E41:O41)</f>
+        <v>269</v>
       </c>
     </row>
   </sheetData>

--- a/计分.xlsx
+++ b/计分.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\life\board_game\project_six_dynasty\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1277F284-95E3-4D3D-9D77-886829F7D517}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86185E70-9A6D-4C72-B47C-628D2EBB7EDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{8AF991C0-2FFC-4B9D-8DFA-610AA56EBD09}"/>
   </bookViews>
@@ -16,7 +16,6 @@
     <sheet name="0516_game" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -40,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="54">
   <si>
     <t>计分</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -227,6 +226,34 @@
   </si>
   <si>
     <t>紫色/刘裕</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">v0.7_0620 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>t10结束阶段，黑色vp达到150结束</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蓝色/郗鉴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v0.8_0627</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>t9 结束，黑色达到150vp结束</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黑色/拓跋</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>紫色/郗鉴</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -611,7 +638,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42E67ED8-6937-492E-8350-3FCD992CF871}">
-  <dimension ref="A1:P41"/>
+  <dimension ref="A1:P55"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.3">
@@ -1073,15 +1100,15 @@
         <v>4</v>
       </c>
       <c r="N18">
-        <f>CEILING(L$17/10,1)*M11</f>
-        <v>40</v>
+        <f>INT(L17/10)*M18</f>
+        <v>36</v>
       </c>
       <c r="O18">
         <v>30</v>
       </c>
       <c r="P18">
         <f>SUM(E18:O18)</f>
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.3">
@@ -1110,15 +1137,15 @@
         <v>4</v>
       </c>
       <c r="N19">
-        <f>CEILING(L$17/10,1)*M12</f>
-        <v>40</v>
+        <f>INT(L17/10)*M19</f>
+        <v>36</v>
       </c>
       <c r="O19">
         <v>14</v>
       </c>
       <c r="P19">
         <f>SUM(E19:O19)</f>
-        <v>163</v>
+        <v>159</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.3">
@@ -1153,15 +1180,15 @@
         <v>4</v>
       </c>
       <c r="N20">
-        <f>CEILING(L$17/10,1)*M13</f>
-        <v>40</v>
+        <f>INT(L17/10)*M20</f>
+        <v>36</v>
       </c>
       <c r="O20">
         <v>18</v>
       </c>
       <c r="P20">
         <f>SUM(E20:O20)</f>
-        <v>181</v>
+        <v>177</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.3">
@@ -1252,15 +1279,15 @@
         <v>4</v>
       </c>
       <c r="N25">
-        <f>CEILING(L24/10,1)*M25</f>
-        <v>68</v>
+        <f>INT(L24/10)*M25</f>
+        <v>64</v>
       </c>
       <c r="O25">
         <v>32</v>
       </c>
       <c r="P25">
         <f>SUM(E25:O25)</f>
-        <v>219</v>
+        <v>215</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.3">
@@ -1298,15 +1325,15 @@
         <v>3</v>
       </c>
       <c r="N26">
-        <f>CEILING(L24/10,1)*M26</f>
-        <v>51</v>
+        <f>INT(L24/10)*M26</f>
+        <v>48</v>
       </c>
       <c r="O26">
         <v>0</v>
       </c>
       <c r="P26">
         <f>SUM(E26:O26)</f>
-        <v>175</v>
+        <v>172</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.3">
@@ -1347,15 +1374,15 @@
         <v>4</v>
       </c>
       <c r="N27">
-        <f>CEILING(L24/10,1)*M27</f>
-        <v>68</v>
+        <f>INT(L24/10)*M27</f>
+        <v>64</v>
       </c>
       <c r="O27">
         <v>6</v>
       </c>
       <c r="P27">
         <f>SUM(E27:O27)</f>
-        <v>227</v>
+        <v>223</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.3">
@@ -1443,15 +1470,15 @@
         <v>4</v>
       </c>
       <c r="N32">
-        <f>CEILING(L31/10,1)*M32</f>
-        <v>52</v>
+        <f>INT(L31/10)*M32</f>
+        <v>48</v>
       </c>
       <c r="O32">
         <v>30</v>
       </c>
       <c r="P32">
         <f>SUM(E32:O32)</f>
-        <v>198</v>
+        <v>194</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.3">
@@ -1486,15 +1513,15 @@
         <v>3</v>
       </c>
       <c r="N33">
-        <f>CEILING(L31/10,1)*M33</f>
-        <v>39</v>
+        <f>INT(L31/10)*M33</f>
+        <v>36</v>
       </c>
       <c r="O33">
         <v>26</v>
       </c>
       <c r="P33">
         <f>SUM(E33:O33)</f>
-        <v>243</v>
+        <v>240</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.3">
@@ -1529,15 +1556,15 @@
         <v>4</v>
       </c>
       <c r="N34">
-        <f>CEILING(L31/10,1)*M34</f>
-        <v>52</v>
+        <f>INT(L31/10)*M34</f>
+        <v>48</v>
       </c>
       <c r="O34">
         <v>34</v>
       </c>
       <c r="P34">
         <f>SUM(E34:O34)</f>
-        <v>246</v>
+        <v>242</v>
       </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.3">
@@ -1619,7 +1646,7 @@
         <v>4</v>
       </c>
       <c r="N39">
-        <f>CEILING(L38/10,1)*M39</f>
+        <f>INT(L38/10)*M39</f>
         <v>52</v>
       </c>
       <c r="O39">
@@ -1665,7 +1692,7 @@
         <v>1</v>
       </c>
       <c r="N40">
-        <f>CEILING(L38/10,1)*M40</f>
+        <f>INT(L38/10)*M40</f>
         <v>13</v>
       </c>
       <c r="O40">
@@ -1702,7 +1729,7 @@
         <v>7</v>
       </c>
       <c r="N41">
-        <f>CEILING(L38/10,1)*M41</f>
+        <f>INT(L38/10)*M41</f>
         <v>91</v>
       </c>
       <c r="O41">
@@ -1711,6 +1738,358 @@
       <c r="P41">
         <f>SUM(E41:O41)</f>
         <v>269</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>47</v>
+      </c>
+      <c r="B43" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>23</v>
+      </c>
+      <c r="H44">
+        <v>4</v>
+      </c>
+      <c r="I44">
+        <v>20</v>
+      </c>
+      <c r="J44">
+        <v>42</v>
+      </c>
+      <c r="K44">
+        <v>156</v>
+      </c>
+      <c r="P44">
+        <f>SUM(E44:O44)</f>
+        <v>222</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>2</v>
+      </c>
+      <c r="H45">
+        <v>13</v>
+      </c>
+      <c r="I45">
+        <v>6</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45">
+        <v>114</v>
+      </c>
+      <c r="L45">
+        <f>SUM(H45:K45)</f>
+        <v>133</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>49</v>
+      </c>
+      <c r="D46">
+        <v>5</v>
+      </c>
+      <c r="G46">
+        <v>29</v>
+      </c>
+      <c r="H46">
+        <v>3</v>
+      </c>
+      <c r="I46">
+        <v>20</v>
+      </c>
+      <c r="J46">
+        <v>11</v>
+      </c>
+      <c r="K46">
+        <v>88</v>
+      </c>
+      <c r="M46">
+        <v>4</v>
+      </c>
+      <c r="N46">
+        <f>INT(L45/10)*M46</f>
+        <v>52</v>
+      </c>
+      <c r="O46">
+        <v>32</v>
+      </c>
+      <c r="P46">
+        <f>SUM(E46:O46)</f>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>37</v>
+      </c>
+      <c r="D47">
+        <v>1</v>
+      </c>
+      <c r="G47">
+        <v>16</v>
+      </c>
+      <c r="H47">
+        <v>1</v>
+      </c>
+      <c r="I47">
+        <v>6</v>
+      </c>
+      <c r="J47">
+        <v>24</v>
+      </c>
+      <c r="K47">
+        <v>113</v>
+      </c>
+      <c r="M47">
+        <v>3</v>
+      </c>
+      <c r="N47">
+        <f>INT(L45/10)*M47</f>
+        <v>39</v>
+      </c>
+      <c r="O47">
+        <v>34</v>
+      </c>
+      <c r="P47">
+        <f>SUM(E47:O47)</f>
+        <v>236</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>38</v>
+      </c>
+      <c r="B48">
+        <v>3</v>
+      </c>
+      <c r="D48">
+        <v>2</v>
+      </c>
+      <c r="E48">
+        <v>2</v>
+      </c>
+      <c r="G48">
+        <v>22</v>
+      </c>
+      <c r="H48">
+        <v>7</v>
+      </c>
+      <c r="I48">
+        <v>20</v>
+      </c>
+      <c r="J48">
+        <v>56</v>
+      </c>
+      <c r="K48">
+        <v>76</v>
+      </c>
+      <c r="M48">
+        <v>5</v>
+      </c>
+      <c r="N48">
+        <f>INT(L45/10)*M48</f>
+        <v>65</v>
+      </c>
+      <c r="O48">
+        <v>24</v>
+      </c>
+      <c r="P48">
+        <f>SUM(E48:O48)</f>
+        <v>277</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>50</v>
+      </c>
+      <c r="B50" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>52</v>
+      </c>
+      <c r="H51">
+        <v>13</v>
+      </c>
+      <c r="I51">
+        <v>44</v>
+      </c>
+      <c r="J51">
+        <v>0</v>
+      </c>
+      <c r="K51">
+        <v>187</v>
+      </c>
+      <c r="P51">
+        <f>SUM(E51:O51)</f>
+        <v>244</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>2</v>
+      </c>
+      <c r="H52">
+        <v>15</v>
+      </c>
+      <c r="I52">
+        <v>16</v>
+      </c>
+      <c r="J52">
+        <v>0</v>
+      </c>
+      <c r="K52">
+        <v>112</v>
+      </c>
+      <c r="L52">
+        <f>SUM(H52:K52)</f>
+        <v>143</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>36</v>
+      </c>
+      <c r="B53">
+        <v>1</v>
+      </c>
+      <c r="C53">
+        <v>2</v>
+      </c>
+      <c r="D53">
+        <v>1</v>
+      </c>
+      <c r="E53">
+        <v>7</v>
+      </c>
+      <c r="F53">
+        <v>7</v>
+      </c>
+      <c r="G53">
+        <v>3</v>
+      </c>
+      <c r="H53">
+        <v>0</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>0</v>
+      </c>
+      <c r="K53">
+        <v>118</v>
+      </c>
+      <c r="M53">
+        <v>2</v>
+      </c>
+      <c r="N53">
+        <f>INT(L52/10)*M53</f>
+        <v>28</v>
+      </c>
+      <c r="O53">
+        <v>0</v>
+      </c>
+      <c r="P53">
+        <f>SUM(E53:O53)</f>
+        <v>165</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>33</v>
+      </c>
+      <c r="B54">
+        <v>3</v>
+      </c>
+      <c r="D54">
+        <v>2</v>
+      </c>
+      <c r="E54">
+        <v>11</v>
+      </c>
+      <c r="G54">
+        <v>7</v>
+      </c>
+      <c r="H54">
+        <v>0</v>
+      </c>
+      <c r="I54">
+        <v>6</v>
+      </c>
+      <c r="J54">
+        <v>3</v>
+      </c>
+      <c r="K54">
+        <v>83</v>
+      </c>
+      <c r="M54">
+        <v>4</v>
+      </c>
+      <c r="N54">
+        <f>INT(L52/10)*M54</f>
+        <v>56</v>
+      </c>
+      <c r="O54">
+        <v>10</v>
+      </c>
+      <c r="P54">
+        <f>SUM(E54:O54)</f>
+        <v>180</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>53</v>
+      </c>
+      <c r="C55">
+        <v>1</v>
+      </c>
+      <c r="D55">
+        <v>1</v>
+      </c>
+      <c r="F55">
+        <v>4</v>
+      </c>
+      <c r="G55">
+        <v>3</v>
+      </c>
+      <c r="H55">
+        <v>2</v>
+      </c>
+      <c r="I55">
+        <v>11</v>
+      </c>
+      <c r="J55">
+        <v>0</v>
+      </c>
+      <c r="K55">
+        <v>48</v>
+      </c>
+      <c r="M55">
+        <v>6</v>
+      </c>
+      <c r="N55">
+        <f>INT(L52/10)*M55</f>
+        <v>84</v>
+      </c>
+      <c r="O55">
+        <v>32</v>
+      </c>
+      <c r="P55">
+        <f>SUM(E55:O55)</f>
+        <v>190</v>
       </c>
     </row>
   </sheetData>
